--- a/DataTables/DetailText/剧情/004_01老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师来访.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E18458C-5F43-4AD7-A620-6E2BC0C4766B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D027D230-3F84-431A-A3FB-AF7082E2EC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="45">
   <si>
     <t>StoryID</t>
   </si>
@@ -289,10 +289,6 @@
   </si>
   <si>
     <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -816,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
@@ -830,15 +826,14 @@
     <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -858,13 +853,13 @@
         <v>16</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>35</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>17</v>
@@ -872,28 +867,25 @@
       <c r="K1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>36</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>33</v>
       </c>
       <c r="N1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="19" t="s">
-        <v>38</v>
+      <c r="O1" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="P1" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q1" s="18" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="54" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>31</v>
@@ -916,66 +908,65 @@
       <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="b">
+      <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="P2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="10"/>
       <c r="H3" s="17"/>
-      <c r="P3" s="11"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="10"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="10"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H7" s="17"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="17"/>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.4">
@@ -1103,7 +1094,7 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1169,7 +1160,7 @@
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/004_01老师来访.xlsx
+++ b/DataTables/DetailText/剧情/004_01老师来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D027D230-3F84-431A-A3FB-AF7082E2EC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDA35EB-60D8-46E8-AB07-02D98863F63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
   <si>
     <t>StoryID</t>
   </si>
@@ -98,10 +87,6 @@
   </si>
   <si>
     <t>NpcID</t>
-  </si>
-  <si>
-    <t>TriggerNpcID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PlayOnce</t>
@@ -312,10 +297,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen_before.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>004_01</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -344,6 +325,18 @@
   </si>
   <si>
     <t>正好我这几日不怎么舒服，东璧你给我看看。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Disease</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>心阳虚</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -351,11 +344,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -369,7 +362,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -390,7 +383,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -534,7 +527,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -813,27 +806,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -847,57 +840,57 @@
         <v>15</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>17</v>
       </c>
       <c r="K1" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="O1" s="18" t="s">
-        <v>19</v>
-      </c>
       <c r="P1" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="54">
+      <c r="A2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="54" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1">
         <v>3</v>
@@ -908,11 +901,13 @@
       <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="L2" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -923,62 +918,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="17"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16">
       <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16">
       <c r="H7" s="17"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16">
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16">
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16">
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16">
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16">
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16">
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16">
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16">
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16">
       <c r="H16" s="17"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8">
       <c r="H17" s="17"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8">
       <c r="H18" s="17"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8">
       <c r="H19" s="17"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="17"/>
     </row>
   </sheetData>
@@ -990,20 +985,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1029,7 +1024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1037,23 +1032,23 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1061,21 +1056,21 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1083,21 +1078,21 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1105,21 +1100,21 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1127,21 +1122,21 @@
         <v>6</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1149,18 +1144,18 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
